--- a/prizmer/static/excel/electric_template_for_load.xlsx
+++ b/prizmer/static/excel/electric_template_for_load.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="63">
   <si>
     <t xml:space="preserve">Населенный пункт</t>
   </si>
@@ -217,19 +217,32 @@
   <si>
     <t xml:space="preserve">МИРТЕК-32-РУ-D37</t>
   </si>
+  <si>
+    <t xml:space="preserve">Квартира 0099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11696196763185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Энергомера СЕ102 R51 </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="000"/>
     <numFmt numFmtId="167" formatCode="[$-419]General"/>
     <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="@"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -311,6 +324,12 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -391,7 +410,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -509,6 +528,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -625,37 +656,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -728,7 +759,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.14"/>
@@ -737,7 +768,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="6.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="10.71"/>
@@ -1380,8 +1411,57 @@
       <c r="Y14" s="26"/>
       <c r="Z14" s="26"/>
     </row>
+    <row r="15" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="L15" s="15" t="n">
+        <v>4002</v>
+      </c>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="Q15" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="26"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="26"/>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="26"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="Q8:Z8"/>
     <mergeCell ref="Q9:Z9"/>
     <mergeCell ref="Q10:Z10"/>
@@ -1389,13 +1469,20 @@
     <mergeCell ref="Q12:Z12"/>
     <mergeCell ref="Q13:Z13"/>
     <mergeCell ref="Q14:Z14"/>
+    <mergeCell ref="Q15:Z15"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G9">
     <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
     <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D9 G1:G1048576">
+  <conditionalFormatting sqref="D8:D9 G16:G1048576 G1:G14">
     <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/prizmer/static/excel/electric_template_for_load.xlsx
+++ b/prizmer/static/excel/electric_template_for_load.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
   <si>
     <t xml:space="preserve">Населенный пункт</t>
   </si>
@@ -228,6 +228,15 @@
   </si>
   <si>
     <t xml:space="preserve">Энергомера СЕ102 R51 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корпус 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 0007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE207 СПОДЭС </t>
   </si>
 </sst>
 </file>
@@ -531,11 +540,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -759,7 +768,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.14"/>
@@ -1460,8 +1469,57 @@
       <c r="Y15" s="26"/>
       <c r="Z15" s="26"/>
     </row>
+    <row r="16" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15" t="n">
+        <v>183293799</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>3799</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>4002</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="Q16" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
+      <c r="V16" s="26"/>
+      <c r="W16" s="26"/>
+      <c r="X16" s="26"/>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="26"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="Q8:Z8"/>
     <mergeCell ref="Q9:Z9"/>
     <mergeCell ref="Q10:Z10"/>
@@ -1470,6 +1528,7 @@
     <mergeCell ref="Q13:Z13"/>
     <mergeCell ref="Q14:Z14"/>
     <mergeCell ref="Q15:Z15"/>
+    <mergeCell ref="Q16:Z16"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G9">
     <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>

--- a/prizmer/static/excel/electric_template_for_load.xlsx
+++ b/prizmer/static/excel/electric_template_for_load.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="68">
   <si>
     <t xml:space="preserve">Населенный пункт</t>
   </si>
@@ -237,6 +237,12 @@
   </si>
   <si>
     <t xml:space="preserve">CE207 СПОДЭС </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квартира 0117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE307 СПОДЭС </t>
   </si>
 </sst>
 </file>
@@ -768,7 +774,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.14"/>
@@ -1518,8 +1524,57 @@
       <c r="Y16" s="26"/>
       <c r="Z16" s="26"/>
     </row>
+    <row r="17" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15" t="n">
+        <v>183231231</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>1231</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>4002</v>
+      </c>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="Q17" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="R17" s="26"/>
+      <c r="S17" s="26"/>
+      <c r="T17" s="26"/>
+      <c r="U17" s="26"/>
+      <c r="V17" s="26"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="26"/>
+      <c r="Y17" s="26"/>
+      <c r="Z17" s="26"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="Q8:Z8"/>
     <mergeCell ref="Q9:Z9"/>
     <mergeCell ref="Q10:Z10"/>
@@ -1529,12 +1584,13 @@
     <mergeCell ref="Q14:Z14"/>
     <mergeCell ref="Q15:Z15"/>
     <mergeCell ref="Q16:Z16"/>
+    <mergeCell ref="Q17:Z17"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G9">
     <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
     <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D9 G16:G1048576 G1:G14">
+  <conditionalFormatting sqref="D8:D9 G1:G14 G16:G1048576">
     <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15">
